--- a/output/pdf_financials_xlsx/RW.xlsx
+++ b/output/pdf_financials_xlsx/RW.xlsx
@@ -931,10 +931,10 @@
         <v>1.250348</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.400496</v>
+        <v>1.413918</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.900695</v>
+        <v>1.93608</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>2.118687</v>
@@ -989,10 +989,10 @@
         <v>0.294607</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.250876</v>
+        <v>0.237454</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.349106</v>
+        <v>-0.384491</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.003432</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.409531</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.094862</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.094862</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.409531</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.094862</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.094862</v>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.425422</v>
+        <v>0.015891</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.188797</v>
+        <v>0.093935</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.04596</v>
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008602</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005776</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008602</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005776</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -40319,7 +40319,11 @@
           <t>Capital lease payments</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E324" s="5" t="n">
         <v>-0.008602</v>
       </c>
@@ -42602,7 +42606,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -46462,7 +46466,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -49751,7 +49755,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -51767,7 +51771,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">

--- a/output/pdf_financials_xlsx/RW.xlsx
+++ b/output/pdf_financials_xlsx/RW.xlsx
@@ -1111,16 +1111,16 @@
         <v>-0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0.028304</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>-0</v>
+        <v>0.016697</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>-0</v>
+        <v>0.012478</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>-0</v>
+        <v>0.07016</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>-0</v>
@@ -2015,16 +2015,16 @@
         <v>-0.360475</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.119748</v>
+        <v>-0.148052</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.828812</v>
+        <v>-0.845509</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.474888</v>
+        <v>-0.487366</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.686095</v>
+        <v>-0.756255</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-0.6089599999999999</v>
@@ -2075,31 +2075,31 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.027518</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.026908</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.018017</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.113569</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.096569</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.081438</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.027073</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.021857</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.019133</v>
       </c>
     </row>
     <row r="29">
@@ -2133,28 +2133,28 @@
         <v>-0.360475</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.119748</v>
+        <v>-0.120534</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.828812</v>
+        <v>-0.818601</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.474888</v>
+        <v>-0.469349</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.686095</v>
+        <v>-0.642686</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.6089599999999999</v>
+        <v>-0.512391</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.32317</v>
+        <v>-1.241732</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.501427</v>
+        <v>-0.474354</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.507294</v>
+        <v>-0.485437</v>
       </c>
       <c r="R29" s="1" t="inlineStr">
         <is>
@@ -2193,28 +2193,28 @@
         <v>-17.08345121969136</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-4.302931432226351</v>
+        <v>-4.331174944483172</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-27.12629713731377</v>
+        <v>-26.79209997309665</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-12.35645246106214</v>
+        <v>-12.21232923583467</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-16.09007977557681</v>
+        <v>-15.07206583730585</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-10.96557609340187</v>
+        <v>-9.226652818041051</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-22.26872865766944</v>
+        <v>-20.89814080847146</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-7.968517311045146</v>
+        <v>-7.538281864685207</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-7.306997487100612</v>
+        <v>-6.992172072103475</v>
       </c>
       <c r="R30" s="1" t="inlineStr">
         <is>
@@ -6241,31 +6241,31 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.027518</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.026908</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.018017</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.113569</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.096569</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.081438</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.027073</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.021857</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.019133</v>
       </c>
     </row>
     <row r="101">
@@ -25926,7 +25926,11 @@
           <t>Depreciation of property, plant and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -28084,7 +28088,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -28674,7 +28682,11 @@
           <t>Depreciation of property, plant and equipment (note 11)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -28769,7 +28781,11 @@
           <t>Depreciation of right-of-use asset (note 12)</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -30458,7 +30474,11 @@
           <t>Deprecation of property, plant and equipment (note 10)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -30557,7 +30577,11 @@
           <t>Depreciation of right-of-use asset (note 11)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -32468,7 +32492,11 @@
           <t>Deprecation of property, plant and equipment (note 9)</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -48048,7 +48076,11 @@
           <t>Net finance expense (note 9)</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -49955,7 +49987,11 @@
           <t>Net finance expense (note 10)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -51866,7 +51902,11 @@
           <t>Net finance expense (note 8)</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RW.xlsx
+++ b/output/pdf_financials_xlsx/RW.xlsx
@@ -28482,7 +28482,11 @@
           <t>Proceeds from Private Placement (note 11)</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -30179,7 +30183,11 @@
           <t>Proceeds from Private Placement (note 14)</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -33500,7 +33508,11 @@
           <t>Restricted cash from private placement</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -34785,7 +34797,11 @@
           <t>Restricted cash from private placement (note 20)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -36468,7 +36484,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -37557,7 +37577,11 @@
           <t>Cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -38848,7 +38872,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -39949,7 +39977,11 @@
           <t>Share capital issued pursuant to private placement (note 5)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -41266,7 +41298,11 @@
           <t>Share capital issued pursuant to private placement (note 7)</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E333" s="5" t="n">
         <v>0.5</v>
       </c>
